--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -844,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -856,58 +856,58 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,51 +961,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -844,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -856,58 +856,58 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -973,46 +973,46 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -973,39 +973,39 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
         <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -844,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -856,58 +856,58 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,51 +961,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -844,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -856,58 +856,58 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,51 +961,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44504</v>
+        <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44806</v>
+        <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44504</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>44806</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45818</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3402-2026</t>
+          <t>A 62884-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,14 +812,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46042</v>
+        <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -868,46 +868,46 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 62884-2021</t>
+          <t>A 37011-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44504</v>
+        <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -961,58 +961,58 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 62884-2021 artfynd.xlsx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 62884-2021 karta.png", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 62884-2021 georefererad karta.tif", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 62884-2021 FSC-klagomål.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 62884-2021 FSC-klagomål mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 62884-2021 tillsynsbegäran.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 62884-2021 tillsynsbegäran mail.docx", "A 62884-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 37011-2022</t>
+          <t>A 3402-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44806</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1066,51 +1066,51 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 37011-2022 artfynd.xlsx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/artfynd/A 3402-2026 artfynd.xlsx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 37011-2022 karta.png", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor/A 3402-2026 karta.png", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 37011-2022 georefererad karta.tif", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/kartor_geotiff/A 3402-2026 georefererad karta.tif", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 37011-2022 FSC-klagomål.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomål/A 3402-2026 FSC-klagomål.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 37011-2022 FSC-klagomål mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/klagomålsmail/A 3402-2026 FSC-klagomål mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 37011-2022 tillsynsbegäran.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsyn/A 3402-2026 tillsynsbegäran.docx", "A 3402-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 37011-2022 tillsynsbegäran mail.docx", "A 37011-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1480/tillsynsmail/A 3402-2026 tillsynsbegäran mail.docx", "A 3402-2026")</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45818</v>
+        <v>45085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
         <v>45818</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 28266-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45085</v>
+        <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28266-2025</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45818</v>
+        <v>46190</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt GÖTEBORG.xlsx
+++ b/Översikt GÖTEBORG.xlsx
@@ -601,7 +601,7 @@
         <v>45882</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>45771</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>44504</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44806</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44623</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45818</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27573-2026</t>
+          <t>A 25015-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46190</v>
+        <v>45085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1336,7 +1336,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25015-2023</t>
+          <t>A 27573-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45085</v>
+        <v>46190</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
